--- a/stories/arbres/TREE-SEC-016.xlsx
+++ b/stories/arbres/TREE-SEC-016.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Nora joue sous le pommier avec Papa. Papa montre l'espace. Nora joue dans l'espace montré. Papa, l'adulte, voit. Les pieds restent ici. Les mains jouent ici. Maman pose le tapis.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le train, le bus, ou la voiture.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1676,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pousse le petit train. Dans l'espace montré. Papa, l'adulte, voit. Pieds ici. Mains ici.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1861,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|On joue où ? Dans l'espace montré.</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2034,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora retient : espace montré, adulte voit. Les mains jouent ici, dans l'espace montré. On continue, avec Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2185,6 +2227,11 @@
       <c r="AV7" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2349,6 +2396,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a choisi Tom. Une pomme tombe. Tom vient sous l'arbre. Ils restent dans l'espace montré. L'adulte voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2535,6 +2587,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2697,6 +2754,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Un oiseau chante. C'est le matin. Nora reste dans l'espace montré. Papa voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2921,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3088,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Le bois du train claque. C'est après la sieste. Nora reste dans l'espace montré. L'adulte voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3255,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3422,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Le vent est doux. C'est le soir. Nora reste dans l'espace montré. Papa, l'adulte, voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3589,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3669,6 +3756,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a choisi Léa. L'herbe sent bon. Léa vient sous l'arbre. Ils restent dans l'espace montré. L'adulte voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3855,6 +3947,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4017,6 +4114,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Le bois du train claque. C'est le matin. Nora reste dans l'espace montré. Papa voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4281,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4448,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Le vent est doux. C'est après la sieste. Nora reste dans l'espace montré. L'adulte voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4615,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4782,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Le tapis est doux. C'est le soir. Nora reste dans l'espace montré. Papa, l'adulte, voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4949,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5116,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a choisi Sami. Un oiseau chante. Sami vient sous l'arbre. Ils restent dans l'espace montré. L'adulte voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5175,6 +5307,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5337,6 +5474,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Le vent est doux. C'est le matin. Nora reste dans l'espace montré. Papa voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5499,6 +5641,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5661,6 +5808,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Le tapis est doux. C'est après la sieste. Nora reste dans l'espace montré. L'adulte voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5823,6 +5975,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5985,6 +6142,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Une pomme tombe. C'est le soir. Nora reste dans l'espace montré. Papa, l'adulte, voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6147,6 +6309,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6309,6 +6476,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pousse le petit bus. Dans l'espace montré. Papa, l'adulte, voit. Pieds ici. Mains ici.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6489,6 +6661,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|On joue où ? Dans l'espace montré.</t>
         </is>
       </c>
     </row>
@@ -6657,6 +6834,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora retient : espace montré, adulte voit. Les mains jouent ici, dans l'espace montré. On continue, avec Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6845,6 +7027,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7009,6 +7196,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a choisi Tom. Le bois du train claque. Tom vient sous l'arbre. Ils restent dans l'espace montré. L'adulte voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7195,6 +7387,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7357,6 +7554,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Le bois du train claque. C'est le matin. Nora reste dans l'espace montré. Papa voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7519,6 +7721,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7681,6 +7888,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Le vent est doux. C'est après la sieste. Nora reste dans l'espace montré. L'adulte voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7843,6 +8055,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8005,6 +8222,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Le tapis est doux. C'est le soir. Nora reste dans l'espace montré. Papa, l'adulte, voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8167,6 +8389,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8329,6 +8556,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a choisi Léa. Le vent est doux. Léa vient sous l'arbre. Ils restent dans l'espace montré. L'adulte voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8515,6 +8747,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8677,6 +8914,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Le vent est doux. C'est le matin. Nora reste dans l'espace montré. Papa voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8839,6 +9081,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9001,6 +9248,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Le tapis est doux. C'est après la sieste. Nora reste dans l'espace montré. L'adulte voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9163,6 +9415,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9325,6 +9582,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Une pomme tombe. C'est le soir. Nora reste dans l'espace montré. Papa, l'adulte, voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9487,6 +9749,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9649,6 +9916,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a choisi Sami. Le tapis est doux. Sami vient sous l'arbre. Ils restent dans l'espace montré. L'adulte voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9835,6 +10107,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9997,6 +10274,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Le tapis est doux. C'est le matin. Nora reste dans l'espace montré. Papa voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10159,6 +10441,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10321,6 +10608,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Une pomme tombe. C'est après la sieste. Nora reste dans l'espace montré. L'adulte voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10483,6 +10775,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10645,6 +10942,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. L'herbe sent bon. C'est le soir. Nora reste dans l'espace montré. Papa, l'adulte, voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10807,6 +11109,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10969,6 +11276,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pousse la petite voiture. Dans l'espace montré. Papa, l'adulte, voit. Pieds ici. Mains ici.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11149,6 +11461,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On joue où ? Dans l'espace montré.</t>
         </is>
       </c>
     </row>
@@ -11317,6 +11634,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora retient : espace montré, adulte voit. Les mains jouent ici, dans l'espace montré. On continue, avec Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11505,6 +11827,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -11669,6 +11996,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a choisi Tom. Une pomme tombe. Tom vient sous l'arbre. Ils restent dans l'espace montré. L'adulte voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11855,6 +12187,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12017,6 +12354,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Le vent est doux. C'est le matin. Nora reste dans l'espace montré. Papa voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12179,6 +12521,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12341,6 +12688,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Le tapis est doux. C'est après la sieste. Nora reste dans l'espace montré. L'adulte voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12503,6 +12855,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12665,6 +13022,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Une pomme tombe. C'est le soir. Nora reste dans l'espace montré. Papa, l'adulte, voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12827,6 +13189,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12989,6 +13356,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a choisi Léa. L'herbe sent bon. Léa vient sous l'arbre. Ils restent dans l'espace montré. L'adulte voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13175,6 +13547,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13337,6 +13714,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Le tapis est doux. C'est le matin. Nora reste dans l'espace montré. Papa voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13499,6 +13881,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13661,6 +14048,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Une pomme tombe. C'est après la sieste. Nora reste dans l'espace montré. L'adulte voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13823,6 +14215,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13985,6 +14382,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. L'herbe sent bon. C'est le soir. Nora reste dans l'espace montré. Papa, l'adulte, voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14147,6 +14549,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14309,6 +14716,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a choisi Sami. Un oiseau chante. Sami vient sous l'arbre. Ils restent dans l'espace montré. L'adulte voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14495,6 +14907,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14657,6 +15074,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Une pomme tombe. C'est le matin. Nora reste dans l'espace montré. Papa voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14819,6 +15241,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14981,6 +15408,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. L'herbe sent bon. C'est après la sieste. Nora reste dans l'espace montré. L'adulte voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15143,6 +15575,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15305,6 +15742,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Un oiseau chante. C'est le soir. Nora reste dans l'espace montré. Papa, l'adulte, voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15467,6 +15909,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15485,7 +15932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15516,6 +15963,13 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SEC-016.xlsx
+++ b/stories/arbres/TREE-SEC-016.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Nora joue sous le pommier avec Papa. Papa montre l'espace. Nora joue dans l'espace montré. Papa, l'adulte, voit. Les pieds restent ici. Les mains jouent ici. Maman pose le tapis.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le train, le bus, ou la voiture.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1681,6 +1688,7 @@
           <t>narrateur|Nora pousse le petit train. Dans l'espace montré. Papa, l'adulte, voit. Pieds ici. Mains ici.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1868,6 +1876,7 @@
           <t>narrateur|On joue où ? Dans l'espace montré.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2039,6 +2048,7 @@
           <t>narrateur|Oui. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora retient : espace montré, adulte voit. Les mains jouent ici, dans l'espace montré. On continue, avec Papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2234,6 +2244,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2401,6 +2412,7 @@
           <t>narrateur|Nora a choisi Tom. Une pomme tombe. Tom vient sous l'arbre. Ils restent dans l'espace montré. L'adulte voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2592,6 +2604,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2759,6 +2772,7 @@
           <t>narrateur|C'est le matin. Un oiseau chante. C'est le matin. Nora reste dans l'espace montré. Papa voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2926,6 +2940,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3093,6 +3108,7 @@
           <t>narrateur|C'est après la sieste. Le bois du train claque. C'est après la sieste. Nora reste dans l'espace montré. L'adulte voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3260,6 +3276,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3427,6 +3444,7 @@
           <t>narrateur|C'est le soir. Le vent est doux. C'est le soir. Nora reste dans l'espace montré. Papa, l'adulte, voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3594,6 +3612,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3761,6 +3780,7 @@
           <t>narrateur|Nora a choisi Léa. L'herbe sent bon. Léa vient sous l'arbre. Ils restent dans l'espace montré. L'adulte voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3952,6 +3972,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4119,6 +4140,7 @@
           <t>narrateur|C'est le matin. Le bois du train claque. C'est le matin. Nora reste dans l'espace montré. Papa voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4286,6 +4308,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4453,6 +4476,7 @@
           <t>narrateur|C'est après la sieste. Le vent est doux. C'est après la sieste. Nora reste dans l'espace montré. L'adulte voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4620,6 +4644,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4787,6 +4812,7 @@
           <t>narrateur|C'est le soir. Le tapis est doux. C'est le soir. Nora reste dans l'espace montré. Papa, l'adulte, voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4954,6 +4980,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5121,6 +5148,7 @@
           <t>narrateur|Nora a choisi Sami. Un oiseau chante. Sami vient sous l'arbre. Ils restent dans l'espace montré. L'adulte voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5312,6 +5340,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5479,6 +5508,7 @@
           <t>narrateur|C'est le matin. Le vent est doux. C'est le matin. Nora reste dans l'espace montré. Papa voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5646,6 +5676,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5813,6 +5844,7 @@
           <t>narrateur|C'est après la sieste. Le tapis est doux. C'est après la sieste. Nora reste dans l'espace montré. L'adulte voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5980,6 +6012,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6147,6 +6180,7 @@
           <t>narrateur|C'est le soir. Une pomme tombe. C'est le soir. Nora reste dans l'espace montré. Papa, l'adulte, voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6314,6 +6348,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6481,6 +6516,7 @@
           <t>narrateur|Nora pousse le petit bus. Dans l'espace montré. Papa, l'adulte, voit. Pieds ici. Mains ici.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6668,6 +6704,7 @@
           <t>narrateur|On joue où ? Dans l'espace montré.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6839,6 +6876,7 @@
           <t>narrateur|Oui. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora retient : espace montré, adulte voit. Les mains jouent ici, dans l'espace montré. On continue, avec Papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7034,6 +7072,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7201,6 +7240,7 @@
           <t>narrateur|Nora a choisi Tom. Le bois du train claque. Tom vient sous l'arbre. Ils restent dans l'espace montré. L'adulte voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7392,6 +7432,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7559,6 +7600,7 @@
           <t>narrateur|C'est le matin. Le bois du train claque. C'est le matin. Nora reste dans l'espace montré. Papa voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7726,6 +7768,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7893,6 +7936,7 @@
           <t>narrateur|C'est après la sieste. Le vent est doux. C'est après la sieste. Nora reste dans l'espace montré. L'adulte voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8060,6 +8104,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8227,6 +8272,7 @@
           <t>narrateur|C'est le soir. Le tapis est doux. C'est le soir. Nora reste dans l'espace montré. Papa, l'adulte, voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8394,6 +8440,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8561,6 +8608,7 @@
           <t>narrateur|Nora a choisi Léa. Le vent est doux. Léa vient sous l'arbre. Ils restent dans l'espace montré. L'adulte voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8752,6 +8800,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8919,6 +8968,7 @@
           <t>narrateur|C'est le matin. Le vent est doux. C'est le matin. Nora reste dans l'espace montré. Papa voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9086,6 +9136,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9253,6 +9304,7 @@
           <t>narrateur|C'est après la sieste. Le tapis est doux. C'est après la sieste. Nora reste dans l'espace montré. L'adulte voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9420,6 +9472,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9587,6 +9640,7 @@
           <t>narrateur|C'est le soir. Une pomme tombe. C'est le soir. Nora reste dans l'espace montré. Papa, l'adulte, voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9754,6 +9808,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9921,6 +9976,7 @@
           <t>narrateur|Nora a choisi Sami. Le tapis est doux. Sami vient sous l'arbre. Ils restent dans l'espace montré. L'adulte voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10112,6 +10168,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10279,6 +10336,7 @@
           <t>narrateur|C'est le matin. Le tapis est doux. C'est le matin. Nora reste dans l'espace montré. Papa voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10446,6 +10504,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10613,6 +10672,7 @@
           <t>narrateur|C'est après la sieste. Une pomme tombe. C'est après la sieste. Nora reste dans l'espace montré. L'adulte voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10780,6 +10840,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10947,6 +11008,7 @@
           <t>narrateur|C'est le soir. L'herbe sent bon. C'est le soir. Nora reste dans l'espace montré. Papa, l'adulte, voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11114,6 +11176,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11281,6 +11344,7 @@
           <t>narrateur|Nora pousse la petite voiture. Dans l'espace montré. Papa, l'adulte, voit. Pieds ici. Mains ici.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11468,6 +11532,7 @@
           <t>narrateur|On joue où ? Dans l'espace montré.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11639,6 +11704,7 @@
           <t>narrateur|Oui. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora retient : espace montré, adulte voit. Les mains jouent ici, dans l'espace montré. On continue, avec Papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11834,6 +11900,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12001,6 +12068,7 @@
           <t>narrateur|Nora a choisi Tom. Une pomme tombe. Tom vient sous l'arbre. Ils restent dans l'espace montré. L'adulte voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12192,6 +12260,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12359,6 +12428,7 @@
           <t>narrateur|C'est le matin. Le vent est doux. C'est le matin. Nora reste dans l'espace montré. Papa voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12526,6 +12596,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12693,6 +12764,7 @@
           <t>narrateur|C'est après la sieste. Le tapis est doux. C'est après la sieste. Nora reste dans l'espace montré. L'adulte voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12860,6 +12932,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13027,6 +13100,7 @@
           <t>narrateur|C'est le soir. Une pomme tombe. C'est le soir. Nora reste dans l'espace montré. Papa, l'adulte, voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13194,6 +13268,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13361,6 +13436,7 @@
           <t>narrateur|Nora a choisi Léa. L'herbe sent bon. Léa vient sous l'arbre. Ils restent dans l'espace montré. L'adulte voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13552,6 +13628,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13719,6 +13796,7 @@
           <t>narrateur|C'est le matin. Le tapis est doux. C'est le matin. Nora reste dans l'espace montré. Papa voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13886,6 +13964,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14053,6 +14132,7 @@
           <t>narrateur|C'est après la sieste. Une pomme tombe. C'est après la sieste. Nora reste dans l'espace montré. L'adulte voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14220,6 +14300,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14387,6 +14468,7 @@
           <t>narrateur|C'est le soir. L'herbe sent bon. C'est le soir. Nora reste dans l'espace montré. Papa, l'adulte, voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14554,6 +14636,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14721,6 +14804,7 @@
           <t>narrateur|Nora a choisi Sami. Un oiseau chante. Sami vient sous l'arbre. Ils restent dans l'espace montré. L'adulte voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14912,6 +14996,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15079,6 +15164,7 @@
           <t>narrateur|C'est le matin. Une pomme tombe. C'est le matin. Nora reste dans l'espace montré. Papa voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15246,6 +15332,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15413,6 +15500,7 @@
           <t>narrateur|C'est après la sieste. L'herbe sent bon. C'est après la sieste. Nora reste dans l'espace montré. L'adulte voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15580,6 +15668,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15747,6 +15836,7 @@
           <t>narrateur|C'est le soir. Un oiseau chante. C'est le soir. Nora reste dans l'espace montré. Papa, l'adulte, voit. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15914,6 +16004,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15932,7 +16023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15970,6 +16061,20 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15984,7 +16089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16171,6 +16276,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
